--- a/03-Test-Cases/Detailed-test-cases/EspoCRM-Accounts-Test-Cases-v1.0.xlsx
+++ b/03-Test-Cases/Detailed-test-cases/EspoCRM-Accounts-Test-Cases-v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SIDDIQ\EspoCRM-QA-Automation\03-Test-Cases\Detailed-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6824BA86-986C-4B61-9FF8-F6E30C5A31A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DAC2D4-FB68-48C6-A452-8DD9138A42D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="258">
   <si>
     <t>Requirement ID</t>
   </si>
@@ -289,9 +289,6 @@
     <t>Existing Account records should be displayed correctly in the Accounts list.</t>
   </si>
   <si>
-    <t>Test data/preconditions not available</t>
-  </si>
-  <si>
     <t>TC-ACC-011</t>
   </si>
   <si>
@@ -342,6 +339,576 @@
   </si>
   <si>
     <t>Account Name field displayed successfully on the Account form.</t>
+  </si>
+  <si>
+    <t>TC-ACC-012</t>
+  </si>
+  <si>
+    <t>TC-ACC-013</t>
+  </si>
+  <si>
+    <t>TC-ACC-014</t>
+  </si>
+  <si>
+    <t>Verify user can delete an Account</t>
+  </si>
+  <si>
+    <t>TC-ACC-015</t>
+  </si>
+  <si>
+    <t>TC-ACC-016</t>
+  </si>
+  <si>
+    <t>TC-ACC-017</t>
+  </si>
+  <si>
+    <t>FR-ACC-017</t>
+  </si>
+  <si>
+    <t>TS-ACC-017</t>
+  </si>
+  <si>
+    <t>Verify user can view Account details</t>
+  </si>
+  <si>
+    <t>FR-ACC-018</t>
+  </si>
+  <si>
+    <t>TS-ACC-018</t>
+  </si>
+  <si>
+    <t>Verify user can edit Account details</t>
+  </si>
+  <si>
+    <t>Verify edited Account data is saved</t>
+  </si>
+  <si>
+    <t>FR-ACC-019</t>
+  </si>
+  <si>
+    <t>TS-ACC-019</t>
+  </si>
+  <si>
+    <t>Verify Delete action displays confirmation</t>
+  </si>
+  <si>
+    <t>Verify deleted Account cannot be found</t>
+  </si>
+  <si>
+    <t>TC-ACC-018</t>
+  </si>
+  <si>
+    <t>FR-ACC-020</t>
+  </si>
+  <si>
+    <t>TS-ACC-020</t>
+  </si>
+  <si>
+    <t>Verify Duplicate action detects an existing Account</t>
+  </si>
+  <si>
+    <t>TC-ACC-019</t>
+  </si>
+  <si>
+    <t>Verify duplicated Account can be saved after changing data</t>
+  </si>
+  <si>
+    <t>TC-ACC-020</t>
+  </si>
+  <si>
+    <t>FR-ACC-021</t>
+  </si>
+  <si>
+    <t>TS-ACC-021</t>
+  </si>
+  <si>
+    <t>Verify Personal Data option is available</t>
+  </si>
+  <si>
+    <t>TC-ACC-021</t>
+  </si>
+  <si>
+    <t>FR-ACC-022</t>
+  </si>
+  <si>
+    <t>TS-ACC-022</t>
+  </si>
+  <si>
+    <t>Verify Followers section allows a user to be followed</t>
+  </si>
+  <si>
+    <t>TC-ACC-022</t>
+  </si>
+  <si>
+    <t>Verify followed Account appears in Followed filter</t>
+  </si>
+  <si>
+    <t>TC-ACC-023</t>
+  </si>
+  <si>
+    <t>Verify user can unfollow an Account</t>
+  </si>
+  <si>
+    <t>TC-ACC-024</t>
+  </si>
+  <si>
+    <t>Verify unfollowed Account is removed from Followed filter</t>
+  </si>
+  <si>
+    <t>TC-ACC-025</t>
+  </si>
+  <si>
+    <t>FR-ACC-023</t>
+  </si>
+  <si>
+    <t>TS-ACC-023</t>
+  </si>
+  <si>
+    <t>Verify Account Audit Log displays recorded activities</t>
+  </si>
+  <si>
+    <t>TC-ACC-026</t>
+  </si>
+  <si>
+    <t>FR-ACC-024</t>
+  </si>
+  <si>
+    <t>TS-ACC-024</t>
+  </si>
+  <si>
+    <t>Verify User Access displays Read, Edit, Delete and Stream access</t>
+  </si>
+  <si>
+    <t>TC-ACC-027</t>
+  </si>
+  <si>
+    <t>FR-ACC-025</t>
+  </si>
+  <si>
+    <t>TS-ACC-025</t>
+  </si>
+  <si>
+    <t>Verify locked Account cannot be edited</t>
+  </si>
+  <si>
+    <t>TC-ACC-028</t>
+  </si>
+  <si>
+    <t>Verify locked Account can be unlocked</t>
+  </si>
+  <si>
+    <t>TC-ACC-029</t>
+  </si>
+  <si>
+    <t>Verify Account can be edited after unlocking</t>
+  </si>
+  <si>
+    <t>TC-ACC-030</t>
+  </si>
+  <si>
+    <t>FR-ACC-013</t>
+  </si>
+  <si>
+    <t>TS-ACC-013</t>
+  </si>
+  <si>
+    <t>Verify phone number can be saved without country code</t>
+  </si>
+  <si>
+    <t>TC-ACC-031</t>
+  </si>
+  <si>
+    <t>Verify phone number can be saved with India country code</t>
+  </si>
+  <si>
+    <t>TC-ACC-032</t>
+  </si>
+  <si>
+    <t>FR-ACC-016</t>
+  </si>
+  <si>
+    <t>TS-ACC-016</t>
+  </si>
+  <si>
+    <t>Verify All filter displays available Accounts</t>
+  </si>
+  <si>
+    <t>TC-ACC-033</t>
+  </si>
+  <si>
+    <t>Verify Recently Created filter displays recently created Accounts</t>
+  </si>
+  <si>
+    <t>TC-ACC-034</t>
+  </si>
+  <si>
+    <t>Verify Starred filter displays starred Accounts</t>
+  </si>
+  <si>
+    <t>TC-ACC-035</t>
+  </si>
+  <si>
+    <t>Verify Only My filter displays Accounts assigned to current user</t>
+  </si>
+  <si>
+    <t>TC-ACC-036</t>
+  </si>
+  <si>
+    <t>Verify Followed filter displays followed Accounts</t>
+  </si>
+  <si>
+    <t>Audit Log should display activities that are configured to be audited for the Account.</t>
+  </si>
+  <si>
+    <t>User is logged in as an authorized EspoCRM user and an existing Account is available.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Test Account 004.
+3. Observe the Account detail page.</t>
+  </si>
+  <si>
+    <t>Account detail page should open and display the saved Account information correctly.</t>
+  </si>
+  <si>
+    <t>Account detail page opened successfully and saved Account information was displayed correctly.</t>
+  </si>
+  <si>
+    <t>Account Name: Test Account 004
+Description: Day 3 Edit Test</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Test Account 004.
+3. Click Edit.
+4. Modify the Description.
+5. Click Save.</t>
+  </si>
+  <si>
+    <t>Account details should be updated successfully without errors.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Verify the updated Description.
+3. Refresh or reopen the Account.
+4. Verify the Description again.</t>
+  </si>
+  <si>
+    <t>Updated Account information should persist and be displayed correctly after reopening the record.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open the test Account.
+3. Click Delete.
+4. Observe the confirmation message.</t>
+  </si>
+  <si>
+    <t>A confirmation message should be displayed before the Account is deleted.</t>
+  </si>
+  <si>
+    <t>Delete confirmation message appeared successfully.</t>
+  </si>
+  <si>
+    <t>Account Name: Test Account Myonly 001</t>
+  </si>
+  <si>
+    <t>1. Click Delete.
+2. Confirm the deletion.
+3. Observe the result.</t>
+  </si>
+  <si>
+    <t>Account should be removed successfully after confirmation.</t>
+  </si>
+  <si>
+    <t>Account was removed successfully after confirmation.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Search for the deleted Account.</t>
+  </si>
+  <si>
+    <t>The deleted Account should not appear in the search results.</t>
+  </si>
+  <si>
+    <t>No data found when searching for the deleted Account.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Click Duplicate.
+3. Do not change any field.
+4. Click Save.
+5. Observe the system response.</t>
+  </si>
+  <si>
+    <t>System should warn that the record being created might already exist.</t>
+  </si>
+  <si>
+    <t>System displayed the alert "The record you are creating might already exist" and identified Test Account 004.</t>
+  </si>
+  <si>
+    <t>Original Account: Test Account 004
+New Account Name: Test Account Duplicate 001</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Click Duplicate.
+3. Change the Account Name.
+4. Click Save.</t>
+  </si>
+  <si>
+    <t>Duplicated Account should be saved successfully after changing the Account data.</t>
+  </si>
+  <si>
+    <t>Duplicated Account was saved successfully after changing the Account data.</t>
+  </si>
+  <si>
+    <t>Account details were updated successfully and saved without any errors.</t>
+  </si>
+  <si>
+    <t>Updated Description was retained and displayed correctly after reopening the Account.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Test Account 004.
+3. Open the Personal Data section.
+4. Observe the available information.</t>
+  </si>
+  <si>
+    <t>Personal Data section should open successfully and display the available personal data information.</t>
+  </si>
+  <si>
+    <t>Personal Data section opened successfully and Email was displayed as the available personal data.</t>
+  </si>
+  <si>
+    <t>Only Email was available under personal data.</t>
+  </si>
+  <si>
+    <t>Admin should be successfully added as a follower.</t>
+  </si>
+  <si>
+    <t>Account Name: Test Account 004
+Follower: Admin</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Test Account 004.
+3. Open Followers.
+4. Select Admin.
+5. Add/confirm the follower.</t>
+  </si>
+  <si>
+    <t>Admin was successfully added as a follower of Test Account 004.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Select Filters.
+3. Select Followed.
+4. Observe the Accounts displayed.</t>
+  </si>
+  <si>
+    <t>Accounts followed by the current user should be displayed.</t>
+  </si>
+  <si>
+    <t>Test Account 004 was displayed under the Followed filter after Admin was added as a follower.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Open Followers.
+3. Select the existing Admin follower.
+4. Use the Unfollow action.</t>
+  </si>
+  <si>
+    <t>Admin should be successfully removed from the Account's followers.</t>
+  </si>
+  <si>
+    <t>Admin was successfully unfollowed from Test Account 004.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Select Filters.
+3. Select Followed.
+4. Search/observe Test Account 004.</t>
+  </si>
+  <si>
+    <t>Test Account 004 should no longer appear in the Followed filter after the current user unfollows it.</t>
+  </si>
+  <si>
+    <t>No data was displayed after Test Account 004 was unfollowed.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Open Audit Log.
+3. Observe the recorded activities.
+4. Verify whether activities that are configured to be audited for the Account.</t>
+  </si>
+  <si>
+    <t>Audit Log is available and the Account Lock activity is displayed. The Description update is not displayed because auditing is disabled for the Description field. Unlock activity was also not displayed.</t>
+  </si>
+  <si>
+    <t>Description field auditing is disabled. Lock activity was recorded, while Unlock activity was not observed in the Audit Log and requires further investigation.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Test Account 004.
+3. Open User Access.
+4. Observe the available access levels.</t>
+  </si>
+  <si>
+    <t>User Access should display the available Read, Edit, Delete, and Stream access levels.</t>
+  </si>
+  <si>
+    <t>User Access displayed Read, Edit, Delete, and Stream access levels. No permission controls were available to modify them from this screen.</t>
+  </si>
+  <si>
+    <t>Access levels are displayed, but no controls are available to modify permissions from the User Access screen.</t>
+  </si>
+  <si>
+    <t>1. Open the Account.
+2. Lock the Account.
+3. Try to edit the Account.
+4. Attempt to change the Description.</t>
+  </si>
+  <si>
+    <t>Locked Account should not allow editing of Account details.</t>
+  </si>
+  <si>
+    <t>Account was locked successfully and editing the Account details was not permitted.</t>
+  </si>
+  <si>
+    <t>Locked Account prevented modification of Account details.</t>
+  </si>
+  <si>
+    <t>Account should be successfully unlocked.</t>
+  </si>
+  <si>
+    <t>1. Click Edit.
+2. Change Describtion to: Account unlocked - Edit verification.
+3. Click Save.
+4. Reopen the Account.</t>
+  </si>
+  <si>
+    <t>Account should be editable after unlocking, and the updated information should be saved successfully.</t>
+  </si>
+  <si>
+    <t>Account was editable after unlocking, and the updated Description was saved successfully.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Click Edit.
+3. Enter the phone number without selecting a country code.
+4. Click Save.</t>
+  </si>
+  <si>
+    <t>Phone number should be saved successfully without requiring a country code.</t>
+  </si>
+  <si>
+    <t>Phone number was saved successfully without selecting a country code.</t>
+  </si>
+  <si>
+    <t>Phone number should be saved successfully with the India country code.</t>
+  </si>
+  <si>
+    <t>1. Open Test Account 004.
+2. Click Edit.
+3. Enter the phone number with selecting a India country code.
+4. Click Save.</t>
+  </si>
+  <si>
+    <t>Phone number was saved successfully after selecting India (+91).</t>
+  </si>
+  <si>
+    <t>Country: India (+91)
+Phone: 9876543210</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Filters.
+3. Select All.
+4. Observe the Accounts list.</t>
+  </si>
+  <si>
+    <t>All available Account records should be displayed.</t>
+  </si>
+  <si>
+    <t>All available Account records were displayed successfully.</t>
+  </si>
+  <si>
+    <t>Recently created Account records</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Filters.
+3. Select Recently Created.
+4. Observe the Accounts list.</t>
+  </si>
+  <si>
+    <t>Recently created Account records should be displayed.</t>
+  </si>
+  <si>
+    <t>Recently created Account records were displayed successfully.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Filters.
+3. Select Starred.
+4. Observe the Accounts list.</t>
+  </si>
+  <si>
+    <t>Starred Account records should be displayed.</t>
+  </si>
+  <si>
+    <t>Test Account 004 appeared successfully under the Starred filter after it was starred.</t>
+  </si>
+  <si>
+    <t>Test Account 004 was starred before applying the filter.</t>
+  </si>
+  <si>
+    <t>User is logged in as Admin and an Account is assigned to Admin.</t>
+  </si>
+  <si>
+    <t>Account Name: Test Account OnlyMy 001
+Assigned User: Admin</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Filters.
+3. Select Only My.
+4. Observe the Accounts list.</t>
+  </si>
+  <si>
+    <t>Accounts assigned to the current user should be displayed.</t>
+  </si>
+  <si>
+    <t>Test Account OnlyMy 001 appeared successfully under the Only My filter because it was assigned to Admin, the current user.</t>
+  </si>
+  <si>
+    <t>Admin was the only available user in the Assigned User list during testing.</t>
+  </si>
+  <si>
+    <t>User is logged in as an authorized EspoCRM user and at least one Account is followed.</t>
+  </si>
+  <si>
+    <t>1. Navigate to Accounts.
+2. Open Filters.
+3. Select Followed.
+4. Observe the Accounts list.</t>
+  </si>
+  <si>
+    <t>Test Account 004 was displayed successfully under the Followed filter when it was followed by Admin.</t>
+  </si>
+  <si>
+    <t>Validated using an empty Accounts list during initial testing.</t>
+  </si>
+  <si>
+    <t>1. Open the locked Account.
+2. Select Unlock.
+3. Observe the Account status.</t>
+  </si>
+  <si>
+    <t>Account was successfully unlocked.</t>
+  </si>
+  <si>
+    <t>Test Account 004 was followed by Admin before applying the filter.</t>
   </si>
 </sst>
 </file>
@@ -365,7 +932,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -373,18 +940,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,509 +1255,1534 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="29.6640625" customWidth="1"/>
     <col min="8" max="8" width="22.88671875" customWidth="1"/>
     <col min="9" max="9" width="28.6640625" customWidth="1"/>
     <col min="10" max="10" width="23.77734375" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.44140625" customWidth="1"/>
+    <col min="13" max="13" width="26.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="M8" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="K4" t="s">
-        <v>83</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" t="s">
-        <v>83</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M13" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" t="s">
-        <v>83</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="M21" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="M28" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K8" t="s">
-        <v>83</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="M29" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K9" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K10" t="s">
-        <v>83</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="M31" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="M32" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K12" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="H35" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="G15" s="2"/>
+      <c r="M35" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>257</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
